--- a/output/2026-10-02_20_Malesia_Negeri_Sembilan_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-02_20_Malesia_Negeri_Sembilan_Utensilerie_e_Macchine_Utensili.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -531,8 +531,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Distributore/produttore di power tools e hand tools dal 1975 (marchi Devon, Metabo, SATA, Kuani), quotato su Bursa Malaysia dal 1993. Sede a Kuala Lumpur; rete dealer nazionale che copre Negeri Sembilan, nessuna filiale fisica confermata in NS. Telefono/email non reperiti su fonti verificabili. Confermato esistente via hiredly.com, isaham.my, moomoo.com; sito non raggiunto via fetch diretto.</t>
@@ -540,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -582,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-10-02_20_Malesia_Negeri_Sembilan_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-02_20_Malesia_Negeri_Sembilan_Utensilerie_e_Macchine_Utensili.xlsx
@@ -575,7 +575,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Marketplace B2B MRO/industriale (58.000+ referenze incl. utensili), registrato MOF, operativo dal 2017. Sede a Klang, Selangor (fuori Negeri Sembilan); consegna dichiarata su Seremban/Senawang/Nilai/Tuanku Jaafar Industrial Park, nessuna sede fisica in NS - incluso come canale distributivo che copre la zona.</t>
+          <t>Marketplace B2B MRO/industriale (58.000+ referenze incl. utensili), registrato MOF, operativo dal 2017. Sede a Klang, Selangor (fuori Negeri Sembilan); consegna dichiarata su Seremban/Senawang/Nilai/Tuanku Jaafar Industrial Park, nessuna sede fisica in NS - incluso come canale distributivo che copre la zona. [DUPLICATO — vedi anche: 2026-10-02_19_Malesia_Negeri_Sembilan_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
